--- a/unique_countries.xlsx
+++ b/unique_countries.xlsx
@@ -357,17 +357,17 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Income Classification</t>
+          <t>Income_Classification</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Number of Countries</t>
+          <t>Number_of_Countries</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>List of Countries</t>
+          <t>List_of_Countries</t>
         </is>
       </c>
     </row>
